--- a/LoteriasExcel/Lotomania_edt.xlsx
+++ b/LoteriasExcel/Lotomania_edt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3879771F-42B1-424E-8CE6-1331A5FDB43F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AF06308-40C1-49BF-8FF8-7CF05CD6AF4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="59520" yWindow="1395" windowWidth="23610" windowHeight="9420" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="63090" yWindow="5355" windowWidth="18630" windowHeight="9465" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTOMANIA" sheetId="6" r:id="rId1"/>
@@ -475,7 +475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C50A779-EE49-4F4E-A3D3-22C3D200C502}">
-  <dimension ref="A1:V459"/>
+  <dimension ref="A1:V460"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="22" max="22" width="13.06640625" customWidth="1"/>
@@ -30258,68 +30258,133 @@
       </c>
     </row>
     <row r="459" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A459" s="2">
+      <c r="A459">
         <v>2965</v>
       </c>
-      <c r="B459" s="3">
+      <c r="B459">
         <v>5</v>
       </c>
-      <c r="C459" s="3">
+      <c r="C459">
         <v>15</v>
       </c>
-      <c r="D459" s="3">
+      <c r="D459">
         <v>16</v>
       </c>
-      <c r="E459" s="3">
+      <c r="E459">
         <v>22</v>
       </c>
-      <c r="F459" s="3">
+      <c r="F459">
         <v>27</v>
       </c>
-      <c r="G459" s="3">
+      <c r="G459">
         <v>32</v>
       </c>
-      <c r="H459" s="3">
+      <c r="H459">
         <v>40</v>
       </c>
-      <c r="I459" s="3">
+      <c r="I459">
         <v>44</v>
       </c>
-      <c r="J459" s="3">
+      <c r="J459">
         <v>49</v>
       </c>
-      <c r="K459" s="3">
+      <c r="K459">
         <v>52</v>
       </c>
-      <c r="L459" s="3">
+      <c r="L459">
         <v>61</v>
       </c>
-      <c r="M459" s="3">
+      <c r="M459">
         <v>62</v>
       </c>
-      <c r="N459" s="3">
+      <c r="N459">
         <v>63</v>
       </c>
-      <c r="O459" s="3">
+      <c r="O459">
         <v>65</v>
       </c>
-      <c r="P459" s="3">
+      <c r="P459">
         <v>69</v>
       </c>
-      <c r="Q459" s="3">
+      <c r="Q459">
         <v>72</v>
       </c>
-      <c r="R459" s="3">
+      <c r="R459">
         <v>78</v>
       </c>
-      <c r="S459" s="3">
+      <c r="S459">
         <v>83</v>
       </c>
-      <c r="T459" s="3">
+      <c r="T459">
         <v>86</v>
       </c>
-      <c r="U459" s="3">
+      <c r="U459">
         <v>93</v>
+      </c>
+    </row>
+    <row r="460" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A460" s="2">
+        <v>2966</v>
+      </c>
+      <c r="B460" s="3">
+        <v>14</v>
+      </c>
+      <c r="C460" s="3">
+        <v>17</v>
+      </c>
+      <c r="D460" s="3">
+        <v>20</v>
+      </c>
+      <c r="E460" s="3">
+        <v>23</v>
+      </c>
+      <c r="F460" s="3">
+        <v>26</v>
+      </c>
+      <c r="G460" s="3">
+        <v>31</v>
+      </c>
+      <c r="H460" s="3">
+        <v>34</v>
+      </c>
+      <c r="I460" s="3">
+        <v>36</v>
+      </c>
+      <c r="J460" s="3">
+        <v>38</v>
+      </c>
+      <c r="K460" s="3">
+        <v>46</v>
+      </c>
+      <c r="L460" s="3">
+        <v>53</v>
+      </c>
+      <c r="M460" s="3">
+        <v>59</v>
+      </c>
+      <c r="N460" s="3">
+        <v>60</v>
+      </c>
+      <c r="O460" s="3">
+        <v>63</v>
+      </c>
+      <c r="P460" s="3">
+        <v>71</v>
+      </c>
+      <c r="Q460" s="3">
+        <v>73</v>
+      </c>
+      <c r="R460" s="3">
+        <v>77</v>
+      </c>
+      <c r="S460" s="3">
+        <v>84</v>
+      </c>
+      <c r="T460" s="3">
+        <v>95</v>
+      </c>
+      <c r="U460" s="3">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -30328,6 +30393,16 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-09T04:04:08+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -30495,16 +30570,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-09T04:04:08+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -30515,6 +30580,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EF4B058-BA16-41FB-9728-59896EB3A3A3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDEE3BD0-E82A-45EA-BF5A-733EBB4C31D1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -30534,17 +30610,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EF4B058-BA16-41FB-9728-59896EB3A3A3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5603705F-A6C5-47C9-9C54-F9F7DF9013C0}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Lotomania_edt.xlsx
+++ b/LoteriasExcel/Lotomania_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AF06308-40C1-49BF-8FF8-7CF05CD6AF4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2160C7D-0140-48A9-BD07-730F2F4ACE94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="63090" yWindow="5355" windowWidth="18630" windowHeight="9465" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="60300" yWindow="6345" windowWidth="24705" windowHeight="9000" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTOMANIA" sheetId="6" r:id="rId1"/>
@@ -148,13 +148,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -475,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C50A779-EE49-4F4E-A3D3-22C3D200C502}">
-  <dimension ref="A1:V460"/>
+  <dimension ref="A1:V461"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="22" max="22" width="13.06640625" customWidth="1"/>
@@ -30323,68 +30321,133 @@
       </c>
     </row>
     <row r="460" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A460" s="2">
+      <c r="A460">
         <v>2966</v>
       </c>
-      <c r="B460" s="3">
+      <c r="B460">
         <v>14</v>
       </c>
-      <c r="C460" s="3">
+      <c r="C460">
         <v>17</v>
       </c>
-      <c r="D460" s="3">
+      <c r="D460">
         <v>20</v>
       </c>
-      <c r="E460" s="3">
+      <c r="E460">
         <v>23</v>
       </c>
-      <c r="F460" s="3">
+      <c r="F460">
         <v>26</v>
       </c>
-      <c r="G460" s="3">
+      <c r="G460">
         <v>31</v>
       </c>
-      <c r="H460" s="3">
+      <c r="H460">
         <v>34</v>
       </c>
-      <c r="I460" s="3">
+      <c r="I460">
         <v>36</v>
       </c>
-      <c r="J460" s="3">
+      <c r="J460">
         <v>38</v>
       </c>
-      <c r="K460" s="3">
+      <c r="K460">
         <v>46</v>
       </c>
-      <c r="L460" s="3">
+      <c r="L460">
         <v>53</v>
       </c>
-      <c r="M460" s="3">
+      <c r="M460">
         <v>59</v>
       </c>
-      <c r="N460" s="3">
+      <c r="N460">
         <v>60</v>
       </c>
-      <c r="O460" s="3">
+      <c r="O460">
         <v>63</v>
       </c>
-      <c r="P460" s="3">
+      <c r="P460">
         <v>71</v>
       </c>
-      <c r="Q460" s="3">
+      <c r="Q460">
         <v>73</v>
       </c>
-      <c r="R460" s="3">
+      <c r="R460">
         <v>77</v>
       </c>
-      <c r="S460" s="3">
+      <c r="S460">
         <v>84</v>
       </c>
-      <c r="T460" s="3">
+      <c r="T460">
         <v>95</v>
       </c>
-      <c r="U460" s="3">
+      <c r="U460">
         <v>97</v>
+      </c>
+    </row>
+    <row r="461" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A461">
+        <v>2967</v>
+      </c>
+      <c r="B461">
+        <v>4</v>
+      </c>
+      <c r="C461">
+        <v>7</v>
+      </c>
+      <c r="D461">
+        <v>10</v>
+      </c>
+      <c r="E461">
+        <v>18</v>
+      </c>
+      <c r="F461">
+        <v>27</v>
+      </c>
+      <c r="G461">
+        <v>29</v>
+      </c>
+      <c r="H461">
+        <v>38</v>
+      </c>
+      <c r="I461">
+        <v>41</v>
+      </c>
+      <c r="J461">
+        <v>44</v>
+      </c>
+      <c r="K461">
+        <v>56</v>
+      </c>
+      <c r="L461">
+        <v>57</v>
+      </c>
+      <c r="M461">
+        <v>67</v>
+      </c>
+      <c r="N461">
+        <v>75</v>
+      </c>
+      <c r="O461">
+        <v>81</v>
+      </c>
+      <c r="P461">
+        <v>85</v>
+      </c>
+      <c r="Q461">
+        <v>90</v>
+      </c>
+      <c r="R461">
+        <v>91</v>
+      </c>
+      <c r="S461">
+        <v>94</v>
+      </c>
+      <c r="T461">
+        <v>96</v>
+      </c>
+      <c r="U461">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -30393,16 +30456,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-09T04:04:08+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -30570,6 +30623,16 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-09T04:04:08+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -30580,17 +30643,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EF4B058-BA16-41FB-9728-59896EB3A3A3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDEE3BD0-E82A-45EA-BF5A-733EBB4C31D1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -30610,6 +30662,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EF4B058-BA16-41FB-9728-59896EB3A3A3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5603705F-A6C5-47C9-9C54-F9F7DF9013C0}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Lotomania_edt.xlsx
+++ b/LoteriasExcel/Lotomania_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2160C7D-0140-48A9-BD07-730F2F4ACE94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B2F4EA0-1681-4B45-B882-5C1B53C0F9DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60300" yWindow="6345" windowWidth="24705" windowHeight="9000" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="69420" yWindow="90" windowWidth="17070" windowHeight="14640" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTOMANIA" sheetId="6" r:id="rId1"/>
@@ -473,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C50A779-EE49-4F4E-A3D3-22C3D200C502}">
-  <dimension ref="A1:V461"/>
+  <dimension ref="A1:V462"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="22" max="22" width="13.06640625" customWidth="1"/>
@@ -30450,12 +30450,87 @@
         <v>98</v>
       </c>
     </row>
+    <row r="462" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A462">
+        <v>2868</v>
+      </c>
+      <c r="B462">
+        <v>0</v>
+      </c>
+      <c r="C462">
+        <v>2</v>
+      </c>
+      <c r="D462">
+        <v>5</v>
+      </c>
+      <c r="E462">
+        <v>13</v>
+      </c>
+      <c r="F462">
+        <v>16</v>
+      </c>
+      <c r="G462">
+        <v>19</v>
+      </c>
+      <c r="H462">
+        <v>30</v>
+      </c>
+      <c r="I462">
+        <v>35</v>
+      </c>
+      <c r="J462">
+        <v>38</v>
+      </c>
+      <c r="K462">
+        <v>43</v>
+      </c>
+      <c r="L462">
+        <v>44</v>
+      </c>
+      <c r="M462">
+        <v>48</v>
+      </c>
+      <c r="N462">
+        <v>56</v>
+      </c>
+      <c r="O462">
+        <v>60</v>
+      </c>
+      <c r="P462">
+        <v>63</v>
+      </c>
+      <c r="Q462">
+        <v>65</v>
+      </c>
+      <c r="R462">
+        <v>74</v>
+      </c>
+      <c r="S462">
+        <v>76</v>
+      </c>
+      <c r="T462">
+        <v>92</v>
+      </c>
+      <c r="U462">
+        <v>95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-09T04:04:08+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -30623,16 +30698,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-09T04:04:08+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -30643,6 +30708,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EF4B058-BA16-41FB-9728-59896EB3A3A3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDEE3BD0-E82A-45EA-BF5A-733EBB4C31D1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -30662,17 +30738,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EF4B058-BA16-41FB-9728-59896EB3A3A3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5603705F-A6C5-47C9-9C54-F9F7DF9013C0}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Lotomania_edt.xlsx
+++ b/LoteriasExcel/Lotomania_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B2F4EA0-1681-4B45-B882-5C1B53C0F9DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B67EB489-A7AE-402D-B27E-8855EE0AB74F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="69420" yWindow="90" windowWidth="17070" windowHeight="14640" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="71835" yWindow="465" windowWidth="14565" windowHeight="13800" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTOMANIA" sheetId="6" r:id="rId1"/>
@@ -473,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C50A779-EE49-4F4E-A3D3-22C3D200C502}">
-  <dimension ref="A1:V462"/>
+  <dimension ref="A1:V463"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="22" max="22" width="13.06640625" customWidth="1"/>
@@ -30515,22 +30515,77 @@
         <v>95</v>
       </c>
     </row>
+    <row r="463" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A463">
+        <v>2969</v>
+      </c>
+      <c r="B463">
+        <v>0</v>
+      </c>
+      <c r="C463">
+        <v>13</v>
+      </c>
+      <c r="D463">
+        <v>15</v>
+      </c>
+      <c r="E463">
+        <v>21</v>
+      </c>
+      <c r="F463">
+        <v>25</v>
+      </c>
+      <c r="G463">
+        <v>38</v>
+      </c>
+      <c r="H463">
+        <v>40</v>
+      </c>
+      <c r="I463">
+        <v>47</v>
+      </c>
+      <c r="J463">
+        <v>55</v>
+      </c>
+      <c r="K463">
+        <v>56</v>
+      </c>
+      <c r="L463">
+        <v>57</v>
+      </c>
+      <c r="M463">
+        <v>58</v>
+      </c>
+      <c r="N463">
+        <v>62</v>
+      </c>
+      <c r="O463">
+        <v>68</v>
+      </c>
+      <c r="P463">
+        <v>70</v>
+      </c>
+      <c r="Q463">
+        <v>75</v>
+      </c>
+      <c r="R463">
+        <v>84</v>
+      </c>
+      <c r="S463">
+        <v>86</v>
+      </c>
+      <c r="T463">
+        <v>90</v>
+      </c>
+      <c r="U463">
+        <v>99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-09T04:04:08+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -30698,6 +30753,16 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-09T04:04:08+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -30708,17 +30773,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EF4B058-BA16-41FB-9728-59896EB3A3A3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDEE3BD0-E82A-45EA-BF5A-733EBB4C31D1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -30738,6 +30792,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EF4B058-BA16-41FB-9728-59896EB3A3A3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5603705F-A6C5-47C9-9C54-F9F7DF9013C0}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Lotomania_edt.xlsx
+++ b/LoteriasExcel/Lotomania_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B67EB489-A7AE-402D-B27E-8855EE0AB74F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8CF201B-6058-4BF8-A3FA-D263402D48D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="71835" yWindow="465" windowWidth="14565" windowHeight="13800" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="62145" yWindow="5790" windowWidth="23730" windowHeight="9660" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTOMANIA" sheetId="6" r:id="rId1"/>
@@ -148,11 +148,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -473,7 +475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C50A779-EE49-4F4E-A3D3-22C3D200C502}">
-  <dimension ref="A1:V463"/>
+  <dimension ref="A1:V467"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="22" max="22" width="13.06640625" customWidth="1"/>
@@ -30580,12 +30582,282 @@
         <v>99</v>
       </c>
     </row>
+    <row r="464" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A464" s="2">
+        <v>2970</v>
+      </c>
+      <c r="B464" s="3">
+        <v>7</v>
+      </c>
+      <c r="C464" s="3">
+        <v>11</v>
+      </c>
+      <c r="D464" s="3">
+        <v>15</v>
+      </c>
+      <c r="E464" s="3">
+        <v>16</v>
+      </c>
+      <c r="F464" s="3">
+        <v>17</v>
+      </c>
+      <c r="G464" s="3">
+        <v>19</v>
+      </c>
+      <c r="H464" s="3">
+        <v>28</v>
+      </c>
+      <c r="I464" s="3">
+        <v>32</v>
+      </c>
+      <c r="J464" s="3">
+        <v>37</v>
+      </c>
+      <c r="K464" s="3">
+        <v>39</v>
+      </c>
+      <c r="L464" s="3">
+        <v>44</v>
+      </c>
+      <c r="M464" s="3">
+        <v>66</v>
+      </c>
+      <c r="N464" s="3">
+        <v>70</v>
+      </c>
+      <c r="O464" s="3">
+        <v>72</v>
+      </c>
+      <c r="P464" s="3">
+        <v>80</v>
+      </c>
+      <c r="Q464" s="3">
+        <v>82</v>
+      </c>
+      <c r="R464" s="3">
+        <v>85</v>
+      </c>
+      <c r="S464" s="3">
+        <v>87</v>
+      </c>
+      <c r="T464" s="3">
+        <v>92</v>
+      </c>
+      <c r="U464" s="3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="465" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A465" s="2">
+        <v>2971</v>
+      </c>
+      <c r="B465" s="3">
+        <v>1</v>
+      </c>
+      <c r="C465" s="3">
+        <v>2</v>
+      </c>
+      <c r="D465" s="3">
+        <v>3</v>
+      </c>
+      <c r="E465" s="3">
+        <v>6</v>
+      </c>
+      <c r="F465" s="3">
+        <v>7</v>
+      </c>
+      <c r="G465" s="3">
+        <v>18</v>
+      </c>
+      <c r="H465" s="3">
+        <v>19</v>
+      </c>
+      <c r="I465" s="3">
+        <v>20</v>
+      </c>
+      <c r="J465" s="3">
+        <v>22</v>
+      </c>
+      <c r="K465" s="3">
+        <v>25</v>
+      </c>
+      <c r="L465" s="3">
+        <v>46</v>
+      </c>
+      <c r="M465" s="3">
+        <v>49</v>
+      </c>
+      <c r="N465" s="3">
+        <v>51</v>
+      </c>
+      <c r="O465" s="3">
+        <v>63</v>
+      </c>
+      <c r="P465" s="3">
+        <v>65</v>
+      </c>
+      <c r="Q465" s="3">
+        <v>68</v>
+      </c>
+      <c r="R465" s="3">
+        <v>69</v>
+      </c>
+      <c r="S465" s="3">
+        <v>86</v>
+      </c>
+      <c r="T465" s="3">
+        <v>88</v>
+      </c>
+      <c r="U465" s="3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="466" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A466" s="2">
+        <v>2972</v>
+      </c>
+      <c r="B466" s="3">
+        <v>6</v>
+      </c>
+      <c r="C466" s="3">
+        <v>10</v>
+      </c>
+      <c r="D466" s="3">
+        <v>16</v>
+      </c>
+      <c r="E466" s="3">
+        <v>17</v>
+      </c>
+      <c r="F466" s="3">
+        <v>21</v>
+      </c>
+      <c r="G466" s="3">
+        <v>31</v>
+      </c>
+      <c r="H466" s="3">
+        <v>33</v>
+      </c>
+      <c r="I466" s="3">
+        <v>35</v>
+      </c>
+      <c r="J466" s="3">
+        <v>38</v>
+      </c>
+      <c r="K466" s="3">
+        <v>41</v>
+      </c>
+      <c r="L466" s="3">
+        <v>45</v>
+      </c>
+      <c r="M466" s="3">
+        <v>51</v>
+      </c>
+      <c r="N466" s="3">
+        <v>52</v>
+      </c>
+      <c r="O466" s="3">
+        <v>76</v>
+      </c>
+      <c r="P466" s="3">
+        <v>77</v>
+      </c>
+      <c r="Q466" s="3">
+        <v>84</v>
+      </c>
+      <c r="R466" s="3">
+        <v>89</v>
+      </c>
+      <c r="S466" s="3">
+        <v>92</v>
+      </c>
+      <c r="T466" s="3">
+        <v>94</v>
+      </c>
+      <c r="U466" s="3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="467" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A467" s="2">
+        <v>2973</v>
+      </c>
+      <c r="B467" s="3">
+        <v>4</v>
+      </c>
+      <c r="C467" s="3">
+        <v>8</v>
+      </c>
+      <c r="D467" s="3">
+        <v>10</v>
+      </c>
+      <c r="E467" s="3">
+        <v>19</v>
+      </c>
+      <c r="F467" s="3">
+        <v>24</v>
+      </c>
+      <c r="G467" s="3">
+        <v>28</v>
+      </c>
+      <c r="H467" s="3">
+        <v>36</v>
+      </c>
+      <c r="I467" s="3">
+        <v>43</v>
+      </c>
+      <c r="J467" s="3">
+        <v>49</v>
+      </c>
+      <c r="K467" s="3">
+        <v>71</v>
+      </c>
+      <c r="L467" s="3">
+        <v>72</v>
+      </c>
+      <c r="M467" s="3">
+        <v>76</v>
+      </c>
+      <c r="N467" s="3">
+        <v>79</v>
+      </c>
+      <c r="O467" s="3">
+        <v>80</v>
+      </c>
+      <c r="P467" s="3">
+        <v>89</v>
+      </c>
+      <c r="Q467" s="3">
+        <v>91</v>
+      </c>
+      <c r="R467" s="3">
+        <v>92</v>
+      </c>
+      <c r="S467" s="3">
+        <v>95</v>
+      </c>
+      <c r="T467" s="3">
+        <v>96</v>
+      </c>
+      <c r="U467" s="3">
+        <v>97</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-09T04:04:08+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -30753,16 +31025,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-09T04:04:08+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -30773,6 +31035,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EF4B058-BA16-41FB-9728-59896EB3A3A3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDEE3BD0-E82A-45EA-BF5A-733EBB4C31D1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -30792,17 +31065,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EF4B058-BA16-41FB-9728-59896EB3A3A3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5603705F-A6C5-47C9-9C54-F9F7DF9013C0}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Lotomania_edt.xlsx
+++ b/LoteriasExcel/Lotomania_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8CF201B-6058-4BF8-A3FA-D263402D48D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{553BB93C-236D-4633-8257-5BE044AD35CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="62145" yWindow="5790" windowWidth="23730" windowHeight="9660" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="4755" yWindow="727" windowWidth="21225" windowHeight="11491" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTOMANIA" sheetId="6" r:id="rId1"/>
@@ -475,7 +475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C50A779-EE49-4F4E-A3D3-22C3D200C502}">
-  <dimension ref="A1:V467"/>
+  <dimension ref="A1:V474"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="22" max="22" width="13.06640625" customWidth="1"/>
@@ -30583,263 +30583,718 @@
       </c>
     </row>
     <row r="464" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A464" s="2">
+      <c r="A464">
         <v>2970</v>
       </c>
-      <c r="B464" s="3">
+      <c r="B464">
         <v>7</v>
       </c>
-      <c r="C464" s="3">
+      <c r="C464">
         <v>11</v>
       </c>
-      <c r="D464" s="3">
+      <c r="D464">
         <v>15</v>
       </c>
-      <c r="E464" s="3">
+      <c r="E464">
         <v>16</v>
       </c>
-      <c r="F464" s="3">
+      <c r="F464">
         <v>17</v>
       </c>
-      <c r="G464" s="3">
+      <c r="G464">
         <v>19</v>
       </c>
-      <c r="H464" s="3">
+      <c r="H464">
         <v>28</v>
       </c>
-      <c r="I464" s="3">
+      <c r="I464">
         <v>32</v>
       </c>
-      <c r="J464" s="3">
+      <c r="J464">
         <v>37</v>
       </c>
-      <c r="K464" s="3">
+      <c r="K464">
         <v>39</v>
       </c>
-      <c r="L464" s="3">
+      <c r="L464">
         <v>44</v>
       </c>
-      <c r="M464" s="3">
+      <c r="M464">
         <v>66</v>
       </c>
-      <c r="N464" s="3">
+      <c r="N464">
         <v>70</v>
       </c>
-      <c r="O464" s="3">
+      <c r="O464">
         <v>72</v>
       </c>
-      <c r="P464" s="3">
+      <c r="P464">
         <v>80</v>
       </c>
-      <c r="Q464" s="3">
+      <c r="Q464">
         <v>82</v>
       </c>
-      <c r="R464" s="3">
+      <c r="R464">
         <v>85</v>
       </c>
-      <c r="S464" s="3">
+      <c r="S464">
         <v>87</v>
       </c>
-      <c r="T464" s="3">
+      <c r="T464">
         <v>92</v>
       </c>
-      <c r="U464" s="3">
+      <c r="U464">
         <v>96</v>
       </c>
     </row>
     <row r="465" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A465" s="2">
+      <c r="A465">
         <v>2971</v>
       </c>
-      <c r="B465" s="3">
+      <c r="B465">
         <v>1</v>
       </c>
-      <c r="C465" s="3">
+      <c r="C465">
         <v>2</v>
       </c>
-      <c r="D465" s="3">
+      <c r="D465">
         <v>3</v>
       </c>
-      <c r="E465" s="3">
+      <c r="E465">
         <v>6</v>
       </c>
-      <c r="F465" s="3">
+      <c r="F465">
         <v>7</v>
       </c>
-      <c r="G465" s="3">
+      <c r="G465">
         <v>18</v>
       </c>
-      <c r="H465" s="3">
+      <c r="H465">
         <v>19</v>
       </c>
-      <c r="I465" s="3">
+      <c r="I465">
         <v>20</v>
       </c>
-      <c r="J465" s="3">
+      <c r="J465">
         <v>22</v>
       </c>
-      <c r="K465" s="3">
+      <c r="K465">
         <v>25</v>
       </c>
-      <c r="L465" s="3">
+      <c r="L465">
         <v>46</v>
       </c>
-      <c r="M465" s="3">
+      <c r="M465">
         <v>49</v>
       </c>
-      <c r="N465" s="3">
+      <c r="N465">
         <v>51</v>
       </c>
-      <c r="O465" s="3">
+      <c r="O465">
         <v>63</v>
       </c>
-      <c r="P465" s="3">
+      <c r="P465">
         <v>65</v>
       </c>
-      <c r="Q465" s="3">
+      <c r="Q465">
         <v>68</v>
       </c>
-      <c r="R465" s="3">
+      <c r="R465">
         <v>69</v>
       </c>
-      <c r="S465" s="3">
+      <c r="S465">
         <v>86</v>
       </c>
-      <c r="T465" s="3">
+      <c r="T465">
         <v>88</v>
       </c>
-      <c r="U465" s="3">
+      <c r="U465">
         <v>92</v>
       </c>
     </row>
     <row r="466" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A466" s="2">
+      <c r="A466">
         <v>2972</v>
       </c>
-      <c r="B466" s="3">
+      <c r="B466">
         <v>6</v>
       </c>
-      <c r="C466" s="3">
+      <c r="C466">
         <v>10</v>
       </c>
-      <c r="D466" s="3">
+      <c r="D466">
         <v>16</v>
       </c>
-      <c r="E466" s="3">
+      <c r="E466">
         <v>17</v>
       </c>
-      <c r="F466" s="3">
+      <c r="F466">
         <v>21</v>
       </c>
-      <c r="G466" s="3">
+      <c r="G466">
         <v>31</v>
       </c>
-      <c r="H466" s="3">
+      <c r="H466">
         <v>33</v>
       </c>
-      <c r="I466" s="3">
+      <c r="I466">
         <v>35</v>
       </c>
-      <c r="J466" s="3">
+      <c r="J466">
         <v>38</v>
       </c>
-      <c r="K466" s="3">
+      <c r="K466">
         <v>41</v>
       </c>
-      <c r="L466" s="3">
+      <c r="L466">
         <v>45</v>
       </c>
-      <c r="M466" s="3">
+      <c r="M466">
         <v>51</v>
       </c>
-      <c r="N466" s="3">
+      <c r="N466">
         <v>52</v>
       </c>
-      <c r="O466" s="3">
+      <c r="O466">
         <v>76</v>
       </c>
-      <c r="P466" s="3">
+      <c r="P466">
         <v>77</v>
       </c>
-      <c r="Q466" s="3">
+      <c r="Q466">
         <v>84</v>
       </c>
-      <c r="R466" s="3">
+      <c r="R466">
         <v>89</v>
       </c>
-      <c r="S466" s="3">
+      <c r="S466">
         <v>92</v>
       </c>
-      <c r="T466" s="3">
+      <c r="T466">
         <v>94</v>
       </c>
-      <c r="U466" s="3">
+      <c r="U466">
         <v>97</v>
       </c>
     </row>
     <row r="467" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A467" s="2">
+      <c r="A467">
         <v>2973</v>
       </c>
-      <c r="B467" s="3">
+      <c r="B467">
         <v>4</v>
       </c>
-      <c r="C467" s="3">
+      <c r="C467">
         <v>8</v>
       </c>
-      <c r="D467" s="3">
+      <c r="D467">
         <v>10</v>
       </c>
-      <c r="E467" s="3">
+      <c r="E467">
         <v>19</v>
       </c>
-      <c r="F467" s="3">
+      <c r="F467">
         <v>24</v>
       </c>
-      <c r="G467" s="3">
+      <c r="G467">
         <v>28</v>
       </c>
-      <c r="H467" s="3">
+      <c r="H467">
         <v>36</v>
       </c>
-      <c r="I467" s="3">
+      <c r="I467">
         <v>43</v>
       </c>
-      <c r="J467" s="3">
+      <c r="J467">
         <v>49</v>
       </c>
-      <c r="K467" s="3">
+      <c r="K467">
         <v>71</v>
       </c>
-      <c r="L467" s="3">
+      <c r="L467">
         <v>72</v>
       </c>
-      <c r="M467" s="3">
+      <c r="M467">
         <v>76</v>
       </c>
-      <c r="N467" s="3">
+      <c r="N467">
         <v>79</v>
       </c>
-      <c r="O467" s="3">
+      <c r="O467">
         <v>80</v>
       </c>
-      <c r="P467" s="3">
+      <c r="P467">
         <v>89</v>
       </c>
-      <c r="Q467" s="3">
+      <c r="Q467">
         <v>91</v>
       </c>
-      <c r="R467" s="3">
+      <c r="R467">
         <v>92</v>
       </c>
-      <c r="S467" s="3">
+      <c r="S467">
         <v>95</v>
       </c>
-      <c r="T467" s="3">
+      <c r="T467">
         <v>96</v>
       </c>
-      <c r="U467" s="3">
+      <c r="U467">
         <v>97</v>
+      </c>
+    </row>
+    <row r="468" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A468" s="2">
+        <v>2974</v>
+      </c>
+      <c r="B468" s="3">
+        <v>3</v>
+      </c>
+      <c r="C468" s="3">
+        <v>7</v>
+      </c>
+      <c r="D468" s="3">
+        <v>10</v>
+      </c>
+      <c r="E468" s="3">
+        <v>13</v>
+      </c>
+      <c r="F468" s="3">
+        <v>20</v>
+      </c>
+      <c r="G468" s="3">
+        <v>23</v>
+      </c>
+      <c r="H468" s="3">
+        <v>26</v>
+      </c>
+      <c r="I468" s="3">
+        <v>29</v>
+      </c>
+      <c r="J468" s="3">
+        <v>31</v>
+      </c>
+      <c r="K468" s="3">
+        <v>37</v>
+      </c>
+      <c r="L468" s="3">
+        <v>42</v>
+      </c>
+      <c r="M468" s="3">
+        <v>46</v>
+      </c>
+      <c r="N468" s="3">
+        <v>47</v>
+      </c>
+      <c r="O468" s="3">
+        <v>58</v>
+      </c>
+      <c r="P468" s="3">
+        <v>59</v>
+      </c>
+      <c r="Q468" s="3">
+        <v>61</v>
+      </c>
+      <c r="R468" s="3">
+        <v>73</v>
+      </c>
+      <c r="S468" s="3">
+        <v>79</v>
+      </c>
+      <c r="T468" s="3">
+        <v>92</v>
+      </c>
+      <c r="U468" s="3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="469" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A469" s="2">
+        <v>2975</v>
+      </c>
+      <c r="B469" s="3">
+        <v>4</v>
+      </c>
+      <c r="C469" s="3">
+        <v>9</v>
+      </c>
+      <c r="D469" s="3">
+        <v>10</v>
+      </c>
+      <c r="E469" s="3">
+        <v>11</v>
+      </c>
+      <c r="F469" s="3">
+        <v>12</v>
+      </c>
+      <c r="G469" s="3">
+        <v>17</v>
+      </c>
+      <c r="H469" s="3">
+        <v>34</v>
+      </c>
+      <c r="I469" s="3">
+        <v>42</v>
+      </c>
+      <c r="J469" s="3">
+        <v>43</v>
+      </c>
+      <c r="K469" s="3">
+        <v>50</v>
+      </c>
+      <c r="L469" s="3">
+        <v>51</v>
+      </c>
+      <c r="M469" s="3">
+        <v>55</v>
+      </c>
+      <c r="N469" s="3">
+        <v>64</v>
+      </c>
+      <c r="O469" s="3">
+        <v>66</v>
+      </c>
+      <c r="P469" s="3">
+        <v>77</v>
+      </c>
+      <c r="Q469" s="3">
+        <v>79</v>
+      </c>
+      <c r="R469" s="3">
+        <v>81</v>
+      </c>
+      <c r="S469" s="3">
+        <v>84</v>
+      </c>
+      <c r="T469" s="3">
+        <v>91</v>
+      </c>
+      <c r="U469" s="3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="470" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A470" s="2">
+        <v>2976</v>
+      </c>
+      <c r="B470" s="3">
+        <v>2</v>
+      </c>
+      <c r="C470" s="3">
+        <v>7</v>
+      </c>
+      <c r="D470" s="3">
+        <v>20</v>
+      </c>
+      <c r="E470" s="3">
+        <v>24</v>
+      </c>
+      <c r="F470" s="3">
+        <v>25</v>
+      </c>
+      <c r="G470" s="3">
+        <v>26</v>
+      </c>
+      <c r="H470" s="3">
+        <v>29</v>
+      </c>
+      <c r="I470" s="3">
+        <v>32</v>
+      </c>
+      <c r="J470" s="3">
+        <v>33</v>
+      </c>
+      <c r="K470" s="3">
+        <v>41</v>
+      </c>
+      <c r="L470" s="3">
+        <v>47</v>
+      </c>
+      <c r="M470" s="3">
+        <v>49</v>
+      </c>
+      <c r="N470" s="3">
+        <v>53</v>
+      </c>
+      <c r="O470" s="3">
+        <v>65</v>
+      </c>
+      <c r="P470" s="3">
+        <v>78</v>
+      </c>
+      <c r="Q470" s="3">
+        <v>79</v>
+      </c>
+      <c r="R470" s="3">
+        <v>91</v>
+      </c>
+      <c r="S470" s="3">
+        <v>92</v>
+      </c>
+      <c r="T470" s="3">
+        <v>93</v>
+      </c>
+      <c r="U470" s="3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="471" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A471" s="2">
+        <v>2977</v>
+      </c>
+      <c r="B471" s="3">
+        <v>1</v>
+      </c>
+      <c r="C471" s="3">
+        <v>5</v>
+      </c>
+      <c r="D471" s="3">
+        <v>9</v>
+      </c>
+      <c r="E471" s="3">
+        <v>12</v>
+      </c>
+      <c r="F471" s="3">
+        <v>15</v>
+      </c>
+      <c r="G471" s="3">
+        <v>18</v>
+      </c>
+      <c r="H471" s="3">
+        <v>21</v>
+      </c>
+      <c r="I471" s="3">
+        <v>30</v>
+      </c>
+      <c r="J471" s="3">
+        <v>37</v>
+      </c>
+      <c r="K471" s="3">
+        <v>38</v>
+      </c>
+      <c r="L471" s="3">
+        <v>41</v>
+      </c>
+      <c r="M471" s="3">
+        <v>42</v>
+      </c>
+      <c r="N471" s="3">
+        <v>44</v>
+      </c>
+      <c r="O471" s="3">
+        <v>46</v>
+      </c>
+      <c r="P471" s="3">
+        <v>47</v>
+      </c>
+      <c r="Q471" s="3">
+        <v>54</v>
+      </c>
+      <c r="R471" s="3">
+        <v>63</v>
+      </c>
+      <c r="S471" s="3">
+        <v>87</v>
+      </c>
+      <c r="T471" s="3">
+        <v>96</v>
+      </c>
+      <c r="U471" s="3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="472" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A472" s="2">
+        <v>2978</v>
+      </c>
+      <c r="B472" s="3">
+        <v>2</v>
+      </c>
+      <c r="C472" s="3">
+        <v>6</v>
+      </c>
+      <c r="D472" s="3">
+        <v>7</v>
+      </c>
+      <c r="E472" s="3">
+        <v>9</v>
+      </c>
+      <c r="F472" s="3">
+        <v>21</v>
+      </c>
+      <c r="G472" s="3">
+        <v>22</v>
+      </c>
+      <c r="H472" s="3">
+        <v>30</v>
+      </c>
+      <c r="I472" s="3">
+        <v>34</v>
+      </c>
+      <c r="J472" s="3">
+        <v>43</v>
+      </c>
+      <c r="K472" s="3">
+        <v>54</v>
+      </c>
+      <c r="L472" s="3">
+        <v>58</v>
+      </c>
+      <c r="M472" s="3">
+        <v>60</v>
+      </c>
+      <c r="N472" s="3">
+        <v>65</v>
+      </c>
+      <c r="O472" s="3">
+        <v>71</v>
+      </c>
+      <c r="P472" s="3">
+        <v>76</v>
+      </c>
+      <c r="Q472" s="3">
+        <v>78</v>
+      </c>
+      <c r="R472" s="3">
+        <v>85</v>
+      </c>
+      <c r="S472" s="3">
+        <v>90</v>
+      </c>
+      <c r="T472" s="3">
+        <v>91</v>
+      </c>
+      <c r="U472" s="3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="473" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A473" s="2">
+        <v>2979</v>
+      </c>
+      <c r="B473" s="3">
+        <v>12</v>
+      </c>
+      <c r="C473" s="3">
+        <v>14</v>
+      </c>
+      <c r="D473" s="3">
+        <v>17</v>
+      </c>
+      <c r="E473" s="3">
+        <v>21</v>
+      </c>
+      <c r="F473" s="3">
+        <v>23</v>
+      </c>
+      <c r="G473" s="3">
+        <v>27</v>
+      </c>
+      <c r="H473" s="3">
+        <v>28</v>
+      </c>
+      <c r="I473" s="3">
+        <v>30</v>
+      </c>
+      <c r="J473" s="3">
+        <v>34</v>
+      </c>
+      <c r="K473" s="3">
+        <v>36</v>
+      </c>
+      <c r="L473" s="3">
+        <v>38</v>
+      </c>
+      <c r="M473" s="3">
+        <v>45</v>
+      </c>
+      <c r="N473" s="3">
+        <v>50</v>
+      </c>
+      <c r="O473" s="3">
+        <v>55</v>
+      </c>
+      <c r="P473" s="3">
+        <v>59</v>
+      </c>
+      <c r="Q473" s="3">
+        <v>73</v>
+      </c>
+      <c r="R473" s="3">
+        <v>74</v>
+      </c>
+      <c r="S473" s="3">
+        <v>90</v>
+      </c>
+      <c r="T473" s="3">
+        <v>92</v>
+      </c>
+      <c r="U473" s="3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="474" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A474" s="2">
+        <v>2980</v>
+      </c>
+      <c r="B474" s="3">
+        <v>6</v>
+      </c>
+      <c r="C474" s="3">
+        <v>13</v>
+      </c>
+      <c r="D474" s="3">
+        <v>16</v>
+      </c>
+      <c r="E474" s="3">
+        <v>25</v>
+      </c>
+      <c r="F474" s="3">
+        <v>33</v>
+      </c>
+      <c r="G474" s="3">
+        <v>38</v>
+      </c>
+      <c r="H474" s="3">
+        <v>40</v>
+      </c>
+      <c r="I474" s="3">
+        <v>48</v>
+      </c>
+      <c r="J474" s="3">
+        <v>56</v>
+      </c>
+      <c r="K474" s="3">
+        <v>57</v>
+      </c>
+      <c r="L474" s="3">
+        <v>68</v>
+      </c>
+      <c r="M474" s="3">
+        <v>78</v>
+      </c>
+      <c r="N474" s="3">
+        <v>79</v>
+      </c>
+      <c r="O474" s="3">
+        <v>80</v>
+      </c>
+      <c r="P474" s="3">
+        <v>85</v>
+      </c>
+      <c r="Q474" s="3">
+        <v>87</v>
+      </c>
+      <c r="R474" s="3">
+        <v>89</v>
+      </c>
+      <c r="S474" s="3">
+        <v>91</v>
+      </c>
+      <c r="T474" s="3">
+        <v>98</v>
+      </c>
+      <c r="U474" s="3">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -30848,16 +31303,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-09T04:04:08+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -31025,6 +31470,16 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-09T04:04:08+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -31035,17 +31490,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EF4B058-BA16-41FB-9728-59896EB3A3A3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDEE3BD0-E82A-45EA-BF5A-733EBB4C31D1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -31065,6 +31509,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EF4B058-BA16-41FB-9728-59896EB3A3A3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5603705F-A6C5-47C9-9C54-F9F7DF9013C0}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Lotomania_edt.xlsx
+++ b/LoteriasExcel/Lotomania_edt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{553BB93C-236D-4633-8257-5BE044AD35CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98C2BD6D-8D7B-46F5-A7DA-0A7D3D63BB72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4755" yWindow="727" windowWidth="21225" windowHeight="11491" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="57510" yWindow="75" windowWidth="19845" windowHeight="11865" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTOMANIA" sheetId="6" r:id="rId1"/>
@@ -475,7 +475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C50A779-EE49-4F4E-A3D3-22C3D200C502}">
-  <dimension ref="A1:V474"/>
+  <dimension ref="A1:V476"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="22" max="22" width="13.06640625" customWidth="1"/>
@@ -30843,458 +30843,588 @@
       </c>
     </row>
     <row r="468" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A468" s="2">
+      <c r="A468">
         <v>2974</v>
       </c>
-      <c r="B468" s="3">
+      <c r="B468">
         <v>3</v>
       </c>
-      <c r="C468" s="3">
+      <c r="C468">
         <v>7</v>
       </c>
-      <c r="D468" s="3">
+      <c r="D468">
         <v>10</v>
       </c>
-      <c r="E468" s="3">
+      <c r="E468">
         <v>13</v>
       </c>
-      <c r="F468" s="3">
+      <c r="F468">
         <v>20</v>
       </c>
-      <c r="G468" s="3">
+      <c r="G468">
         <v>23</v>
       </c>
-      <c r="H468" s="3">
+      <c r="H468">
         <v>26</v>
       </c>
-      <c r="I468" s="3">
+      <c r="I468">
         <v>29</v>
       </c>
-      <c r="J468" s="3">
+      <c r="J468">
         <v>31</v>
       </c>
-      <c r="K468" s="3">
+      <c r="K468">
         <v>37</v>
       </c>
-      <c r="L468" s="3">
+      <c r="L468">
         <v>42</v>
       </c>
-      <c r="M468" s="3">
+      <c r="M468">
         <v>46</v>
       </c>
-      <c r="N468" s="3">
+      <c r="N468">
         <v>47</v>
       </c>
-      <c r="O468" s="3">
+      <c r="O468">
         <v>58</v>
       </c>
-      <c r="P468" s="3">
+      <c r="P468">
         <v>59</v>
       </c>
-      <c r="Q468" s="3">
+      <c r="Q468">
         <v>61</v>
       </c>
-      <c r="R468" s="3">
+      <c r="R468">
         <v>73</v>
       </c>
-      <c r="S468" s="3">
+      <c r="S468">
         <v>79</v>
       </c>
-      <c r="T468" s="3">
+      <c r="T468">
         <v>92</v>
       </c>
-      <c r="U468" s="3">
+      <c r="U468">
         <v>95</v>
       </c>
     </row>
     <row r="469" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A469" s="2">
+      <c r="A469">
         <v>2975</v>
       </c>
-      <c r="B469" s="3">
+      <c r="B469">
         <v>4</v>
       </c>
-      <c r="C469" s="3">
+      <c r="C469">
         <v>9</v>
       </c>
-      <c r="D469" s="3">
+      <c r="D469">
         <v>10</v>
       </c>
-      <c r="E469" s="3">
+      <c r="E469">
         <v>11</v>
       </c>
-      <c r="F469" s="3">
+      <c r="F469">
         <v>12</v>
       </c>
-      <c r="G469" s="3">
+      <c r="G469">
         <v>17</v>
       </c>
-      <c r="H469" s="3">
+      <c r="H469">
         <v>34</v>
       </c>
-      <c r="I469" s="3">
+      <c r="I469">
         <v>42</v>
       </c>
-      <c r="J469" s="3">
+      <c r="J469">
         <v>43</v>
       </c>
-      <c r="K469" s="3">
+      <c r="K469">
         <v>50</v>
       </c>
-      <c r="L469" s="3">
+      <c r="L469">
         <v>51</v>
       </c>
-      <c r="M469" s="3">
+      <c r="M469">
         <v>55</v>
       </c>
-      <c r="N469" s="3">
+      <c r="N469">
         <v>64</v>
       </c>
-      <c r="O469" s="3">
+      <c r="O469">
         <v>66</v>
       </c>
-      <c r="P469" s="3">
+      <c r="P469">
         <v>77</v>
       </c>
-      <c r="Q469" s="3">
+      <c r="Q469">
         <v>79</v>
       </c>
-      <c r="R469" s="3">
+      <c r="R469">
         <v>81</v>
       </c>
-      <c r="S469" s="3">
+      <c r="S469">
         <v>84</v>
       </c>
-      <c r="T469" s="3">
+      <c r="T469">
         <v>91</v>
       </c>
-      <c r="U469" s="3">
+      <c r="U469">
         <v>96</v>
       </c>
     </row>
     <row r="470" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A470" s="2">
+      <c r="A470">
         <v>2976</v>
       </c>
-      <c r="B470" s="3">
+      <c r="B470">
         <v>2</v>
       </c>
-      <c r="C470" s="3">
+      <c r="C470">
         <v>7</v>
       </c>
-      <c r="D470" s="3">
+      <c r="D470">
         <v>20</v>
       </c>
-      <c r="E470" s="3">
+      <c r="E470">
         <v>24</v>
       </c>
-      <c r="F470" s="3">
+      <c r="F470">
         <v>25</v>
       </c>
-      <c r="G470" s="3">
+      <c r="G470">
         <v>26</v>
       </c>
-      <c r="H470" s="3">
+      <c r="H470">
         <v>29</v>
       </c>
-      <c r="I470" s="3">
+      <c r="I470">
         <v>32</v>
       </c>
-      <c r="J470" s="3">
+      <c r="J470">
         <v>33</v>
       </c>
-      <c r="K470" s="3">
+      <c r="K470">
         <v>41</v>
       </c>
-      <c r="L470" s="3">
+      <c r="L470">
         <v>47</v>
       </c>
-      <c r="M470" s="3">
+      <c r="M470">
         <v>49</v>
       </c>
-      <c r="N470" s="3">
+      <c r="N470">
         <v>53</v>
       </c>
-      <c r="O470" s="3">
+      <c r="O470">
         <v>65</v>
       </c>
-      <c r="P470" s="3">
+      <c r="P470">
         <v>78</v>
       </c>
-      <c r="Q470" s="3">
+      <c r="Q470">
         <v>79</v>
       </c>
-      <c r="R470" s="3">
+      <c r="R470">
         <v>91</v>
       </c>
-      <c r="S470" s="3">
+      <c r="S470">
         <v>92</v>
       </c>
-      <c r="T470" s="3">
+      <c r="T470">
         <v>93</v>
       </c>
-      <c r="U470" s="3">
+      <c r="U470">
         <v>95</v>
       </c>
     </row>
     <row r="471" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A471" s="2">
+      <c r="A471">
         <v>2977</v>
       </c>
-      <c r="B471" s="3">
+      <c r="B471">
         <v>1</v>
       </c>
-      <c r="C471" s="3">
+      <c r="C471">
         <v>5</v>
       </c>
-      <c r="D471" s="3">
+      <c r="D471">
         <v>9</v>
       </c>
-      <c r="E471" s="3">
+      <c r="E471">
         <v>12</v>
       </c>
-      <c r="F471" s="3">
+      <c r="F471">
         <v>15</v>
       </c>
-      <c r="G471" s="3">
+      <c r="G471">
         <v>18</v>
       </c>
-      <c r="H471" s="3">
+      <c r="H471">
         <v>21</v>
       </c>
-      <c r="I471" s="3">
+      <c r="I471">
         <v>30</v>
       </c>
-      <c r="J471" s="3">
+      <c r="J471">
         <v>37</v>
       </c>
-      <c r="K471" s="3">
+      <c r="K471">
         <v>38</v>
       </c>
-      <c r="L471" s="3">
+      <c r="L471">
         <v>41</v>
       </c>
-      <c r="M471" s="3">
+      <c r="M471">
         <v>42</v>
       </c>
-      <c r="N471" s="3">
+      <c r="N471">
         <v>44</v>
       </c>
-      <c r="O471" s="3">
+      <c r="O471">
         <v>46</v>
       </c>
-      <c r="P471" s="3">
+      <c r="P471">
         <v>47</v>
       </c>
-      <c r="Q471" s="3">
+      <c r="Q471">
         <v>54</v>
       </c>
-      <c r="R471" s="3">
+      <c r="R471">
         <v>63</v>
       </c>
-      <c r="S471" s="3">
+      <c r="S471">
         <v>87</v>
       </c>
-      <c r="T471" s="3">
+      <c r="T471">
         <v>96</v>
       </c>
-      <c r="U471" s="3">
+      <c r="U471">
         <v>98</v>
       </c>
     </row>
     <row r="472" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A472" s="2">
+      <c r="A472">
         <v>2978</v>
       </c>
-      <c r="B472" s="3">
+      <c r="B472">
         <v>2</v>
       </c>
-      <c r="C472" s="3">
+      <c r="C472">
         <v>6</v>
       </c>
-      <c r="D472" s="3">
+      <c r="D472">
         <v>7</v>
       </c>
-      <c r="E472" s="3">
+      <c r="E472">
         <v>9</v>
       </c>
-      <c r="F472" s="3">
+      <c r="F472">
         <v>21</v>
       </c>
-      <c r="G472" s="3">
+      <c r="G472">
         <v>22</v>
       </c>
-      <c r="H472" s="3">
+      <c r="H472">
         <v>30</v>
       </c>
-      <c r="I472" s="3">
+      <c r="I472">
         <v>34</v>
       </c>
-      <c r="J472" s="3">
+      <c r="J472">
         <v>43</v>
       </c>
-      <c r="K472" s="3">
+      <c r="K472">
         <v>54</v>
       </c>
-      <c r="L472" s="3">
+      <c r="L472">
         <v>58</v>
       </c>
-      <c r="M472" s="3">
+      <c r="M472">
         <v>60</v>
       </c>
-      <c r="N472" s="3">
+      <c r="N472">
         <v>65</v>
       </c>
-      <c r="O472" s="3">
+      <c r="O472">
         <v>71</v>
       </c>
-      <c r="P472" s="3">
+      <c r="P472">
         <v>76</v>
       </c>
-      <c r="Q472" s="3">
+      <c r="Q472">
         <v>78</v>
       </c>
-      <c r="R472" s="3">
+      <c r="R472">
         <v>85</v>
       </c>
-      <c r="S472" s="3">
+      <c r="S472">
         <v>90</v>
       </c>
-      <c r="T472" s="3">
+      <c r="T472">
         <v>91</v>
       </c>
-      <c r="U472" s="3">
+      <c r="U472">
         <v>92</v>
       </c>
     </row>
     <row r="473" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A473" s="2">
+      <c r="A473">
         <v>2979</v>
       </c>
-      <c r="B473" s="3">
+      <c r="B473">
         <v>12</v>
       </c>
-      <c r="C473" s="3">
+      <c r="C473">
         <v>14</v>
       </c>
-      <c r="D473" s="3">
+      <c r="D473">
         <v>17</v>
       </c>
-      <c r="E473" s="3">
+      <c r="E473">
         <v>21</v>
       </c>
-      <c r="F473" s="3">
+      <c r="F473">
         <v>23</v>
       </c>
-      <c r="G473" s="3">
+      <c r="G473">
         <v>27</v>
       </c>
-      <c r="H473" s="3">
+      <c r="H473">
         <v>28</v>
       </c>
-      <c r="I473" s="3">
+      <c r="I473">
         <v>30</v>
       </c>
-      <c r="J473" s="3">
+      <c r="J473">
         <v>34</v>
       </c>
-      <c r="K473" s="3">
+      <c r="K473">
         <v>36</v>
       </c>
-      <c r="L473" s="3">
+      <c r="L473">
         <v>38</v>
       </c>
-      <c r="M473" s="3">
+      <c r="M473">
         <v>45</v>
       </c>
-      <c r="N473" s="3">
+      <c r="N473">
         <v>50</v>
       </c>
-      <c r="O473" s="3">
+      <c r="O473">
         <v>55</v>
       </c>
-      <c r="P473" s="3">
+      <c r="P473">
         <v>59</v>
       </c>
-      <c r="Q473" s="3">
+      <c r="Q473">
         <v>73</v>
       </c>
-      <c r="R473" s="3">
+      <c r="R473">
         <v>74</v>
       </c>
-      <c r="S473" s="3">
+      <c r="S473">
         <v>90</v>
       </c>
-      <c r="T473" s="3">
+      <c r="T473">
         <v>92</v>
       </c>
-      <c r="U473" s="3">
+      <c r="U473">
         <v>94</v>
       </c>
     </row>
     <row r="474" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A474" s="2">
+      <c r="A474">
         <v>2980</v>
       </c>
-      <c r="B474" s="3">
+      <c r="B474">
         <v>6</v>
       </c>
-      <c r="C474" s="3">
+      <c r="C474">
         <v>13</v>
       </c>
-      <c r="D474" s="3">
+      <c r="D474">
         <v>16</v>
       </c>
-      <c r="E474" s="3">
+      <c r="E474">
         <v>25</v>
       </c>
-      <c r="F474" s="3">
+      <c r="F474">
         <v>33</v>
       </c>
-      <c r="G474" s="3">
+      <c r="G474">
         <v>38</v>
       </c>
-      <c r="H474" s="3">
+      <c r="H474">
         <v>40</v>
       </c>
-      <c r="I474" s="3">
+      <c r="I474">
         <v>48</v>
       </c>
-      <c r="J474" s="3">
+      <c r="J474">
         <v>56</v>
       </c>
-      <c r="K474" s="3">
+      <c r="K474">
         <v>57</v>
       </c>
-      <c r="L474" s="3">
+      <c r="L474">
         <v>68</v>
       </c>
-      <c r="M474" s="3">
+      <c r="M474">
         <v>78</v>
       </c>
-      <c r="N474" s="3">
+      <c r="N474">
         <v>79</v>
       </c>
-      <c r="O474" s="3">
+      <c r="O474">
         <v>80</v>
       </c>
-      <c r="P474" s="3">
+      <c r="P474">
         <v>85</v>
       </c>
-      <c r="Q474" s="3">
+      <c r="Q474">
         <v>87</v>
       </c>
-      <c r="R474" s="3">
+      <c r="R474">
         <v>89</v>
       </c>
-      <c r="S474" s="3">
+      <c r="S474">
         <v>91</v>
       </c>
-      <c r="T474" s="3">
+      <c r="T474">
         <v>98</v>
       </c>
-      <c r="U474" s="3">
+      <c r="U474">
         <v>99</v>
+      </c>
+    </row>
+    <row r="475" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A475" s="3">
+        <v>2981</v>
+      </c>
+      <c r="B475" s="2">
+        <v>15</v>
+      </c>
+      <c r="C475" s="2">
+        <v>21</v>
+      </c>
+      <c r="D475" s="2">
+        <v>24</v>
+      </c>
+      <c r="E475" s="2">
+        <v>33</v>
+      </c>
+      <c r="F475" s="2">
+        <v>34</v>
+      </c>
+      <c r="G475" s="2">
+        <v>37</v>
+      </c>
+      <c r="H475" s="2">
+        <v>43</v>
+      </c>
+      <c r="I475" s="2">
+        <v>50</v>
+      </c>
+      <c r="J475" s="2">
+        <v>60</v>
+      </c>
+      <c r="K475" s="2">
+        <v>61</v>
+      </c>
+      <c r="L475" s="2">
+        <v>64</v>
+      </c>
+      <c r="M475" s="2">
+        <v>69</v>
+      </c>
+      <c r="N475" s="2">
+        <v>71</v>
+      </c>
+      <c r="O475" s="2">
+        <v>75</v>
+      </c>
+      <c r="P475" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q475" s="2">
+        <v>81</v>
+      </c>
+      <c r="R475" s="2">
+        <v>86</v>
+      </c>
+      <c r="S475" s="2">
+        <v>96</v>
+      </c>
+      <c r="T475" s="2">
+        <v>97</v>
+      </c>
+      <c r="U475" s="2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="476" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A476" s="3">
+        <v>2982</v>
+      </c>
+      <c r="B476" s="2">
+        <v>2</v>
+      </c>
+      <c r="C476" s="2">
+        <v>3</v>
+      </c>
+      <c r="D476" s="2">
+        <v>4</v>
+      </c>
+      <c r="E476" s="2">
+        <v>7</v>
+      </c>
+      <c r="F476" s="2">
+        <v>8</v>
+      </c>
+      <c r="G476" s="2">
+        <v>13</v>
+      </c>
+      <c r="H476" s="2">
+        <v>16</v>
+      </c>
+      <c r="I476" s="2">
+        <v>27</v>
+      </c>
+      <c r="J476" s="2">
+        <v>32</v>
+      </c>
+      <c r="K476" s="2">
+        <v>33</v>
+      </c>
+      <c r="L476" s="2">
+        <v>57</v>
+      </c>
+      <c r="M476" s="2">
+        <v>59</v>
+      </c>
+      <c r="N476" s="2">
+        <v>61</v>
+      </c>
+      <c r="O476" s="2">
+        <v>64</v>
+      </c>
+      <c r="P476" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q476" s="2">
+        <v>77</v>
+      </c>
+      <c r="R476" s="2">
+        <v>80</v>
+      </c>
+      <c r="S476" s="2">
+        <v>91</v>
+      </c>
+      <c r="T476" s="2">
+        <v>95</v>
+      </c>
+      <c r="U476" s="2">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -31303,6 +31433,16 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-09T04:04:08+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -31470,16 +31610,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-09T04:04:08+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -31490,6 +31620,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EF4B058-BA16-41FB-9728-59896EB3A3A3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDEE3BD0-E82A-45EA-BF5A-733EBB4C31D1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -31509,17 +31650,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EF4B058-BA16-41FB-9728-59896EB3A3A3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5603705F-A6C5-47C9-9C54-F9F7DF9013C0}">
   <ds:schemaRefs>
